--- a/docs/forms/patient_intake_form.xlsx
+++ b/docs/forms/patient_intake_form.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +88,11 @@
       <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -143,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,6 +192,7 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -901,7 +907,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>The clinician who will hold this patient, written as the email address they sign in with. Leave blank to assign them to whoever imports the file. An address the practice does not recognise is reported back rather than guessed at.</t>
+          <t>Pre-filled with heba.moustafa5@gmail.com, so you can leave it as it is. Change it only if a patient belongs to a different clinician, and use the address they sign in with. An address the practice does not recognise is reported back rather than guessed at.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1056,11 @@
         </is>
       </c>
       <c r="I34" s="16" t="inlineStr"/>
-      <c r="J34" s="16" t="inlineStr"/>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1143,7 +1153,11 @@
       <c r="F2" s="19" t="n"/>
       <c r="G2" s="19" t="n"/>
       <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="n"/>
@@ -1154,7 +1168,11 @@
       <c r="F3" s="19" t="n"/>
       <c r="G3" s="19" t="n"/>
       <c r="H3" s="19" t="n"/>
-      <c r="I3" s="19" t="n"/>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="n"/>
@@ -1165,7 +1183,11 @@
       <c r="F4" s="19" t="n"/>
       <c r="G4" s="19" t="n"/>
       <c r="H4" s="19" t="n"/>
-      <c r="I4" s="19" t="n"/>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="n"/>
@@ -1176,7 +1198,11 @@
       <c r="F5" s="19" t="n"/>
       <c r="G5" s="19" t="n"/>
       <c r="H5" s="19" t="n"/>
-      <c r="I5" s="19" t="n"/>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n"/>
@@ -1187,7 +1213,11 @@
       <c r="F6" s="19" t="n"/>
       <c r="G6" s="19" t="n"/>
       <c r="H6" s="19" t="n"/>
-      <c r="I6" s="19" t="n"/>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="n"/>
@@ -1198,7 +1228,11 @@
       <c r="F7" s="19" t="n"/>
       <c r="G7" s="19" t="n"/>
       <c r="H7" s="19" t="n"/>
-      <c r="I7" s="19" t="n"/>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="n"/>
@@ -1209,7 +1243,11 @@
       <c r="F8" s="19" t="n"/>
       <c r="G8" s="19" t="n"/>
       <c r="H8" s="19" t="n"/>
-      <c r="I8" s="19" t="n"/>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
@@ -1220,7 +1258,11 @@
       <c r="F9" s="19" t="n"/>
       <c r="G9" s="19" t="n"/>
       <c r="H9" s="19" t="n"/>
-      <c r="I9" s="19" t="n"/>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
@@ -1231,7 +1273,11 @@
       <c r="F10" s="19" t="n"/>
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
-      <c r="I10" s="19" t="n"/>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="n"/>
@@ -1242,7 +1288,11 @@
       <c r="F11" s="19" t="n"/>
       <c r="G11" s="19" t="n"/>
       <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n"/>
@@ -1253,7 +1303,11 @@
       <c r="F12" s="19" t="n"/>
       <c r="G12" s="19" t="n"/>
       <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n"/>
@@ -1264,7 +1318,11 @@
       <c r="F13" s="19" t="n"/>
       <c r="G13" s="19" t="n"/>
       <c r="H13" s="19" t="n"/>
-      <c r="I13" s="19" t="n"/>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n"/>
@@ -1275,7 +1333,11 @@
       <c r="F14" s="19" t="n"/>
       <c r="G14" s="19" t="n"/>
       <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>
@@ -1286,7 +1348,11 @@
       <c r="F15" s="19" t="n"/>
       <c r="G15" s="19" t="n"/>
       <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n"/>
@@ -1297,7 +1363,11 @@
       <c r="F16" s="19" t="n"/>
       <c r="G16" s="19" t="n"/>
       <c r="H16" s="19" t="n"/>
-      <c r="I16" s="19" t="n"/>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n"/>
@@ -1308,7 +1378,11 @@
       <c r="F17" s="19" t="n"/>
       <c r="G17" s="19" t="n"/>
       <c r="H17" s="19" t="n"/>
-      <c r="I17" s="19" t="n"/>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n"/>
@@ -1319,7 +1393,11 @@
       <c r="F18" s="19" t="n"/>
       <c r="G18" s="19" t="n"/>
       <c r="H18" s="19" t="n"/>
-      <c r="I18" s="19" t="n"/>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n"/>
@@ -1330,7 +1408,11 @@
       <c r="F19" s="19" t="n"/>
       <c r="G19" s="19" t="n"/>
       <c r="H19" s="19" t="n"/>
-      <c r="I19" s="19" t="n"/>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n"/>
@@ -1341,7 +1423,11 @@
       <c r="F20" s="19" t="n"/>
       <c r="G20" s="19" t="n"/>
       <c r="H20" s="19" t="n"/>
-      <c r="I20" s="19" t="n"/>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="n"/>
@@ -1352,7 +1438,11 @@
       <c r="F21" s="19" t="n"/>
       <c r="G21" s="19" t="n"/>
       <c r="H21" s="19" t="n"/>
-      <c r="I21" s="19" t="n"/>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="n"/>
@@ -1363,7 +1453,11 @@
       <c r="F22" s="19" t="n"/>
       <c r="G22" s="19" t="n"/>
       <c r="H22" s="19" t="n"/>
-      <c r="I22" s="19" t="n"/>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n"/>
@@ -1374,7 +1468,11 @@
       <c r="F23" s="19" t="n"/>
       <c r="G23" s="19" t="n"/>
       <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="n"/>
@@ -1385,7 +1483,11 @@
       <c r="F24" s="19" t="n"/>
       <c r="G24" s="19" t="n"/>
       <c r="H24" s="19" t="n"/>
-      <c r="I24" s="19" t="n"/>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="n"/>
@@ -1396,7 +1498,11 @@
       <c r="F25" s="19" t="n"/>
       <c r="G25" s="19" t="n"/>
       <c r="H25" s="19" t="n"/>
-      <c r="I25" s="19" t="n"/>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="n"/>
@@ -1407,7 +1513,11 @@
       <c r="F26" s="19" t="n"/>
       <c r="G26" s="19" t="n"/>
       <c r="H26" s="19" t="n"/>
-      <c r="I26" s="19" t="n"/>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="n"/>
@@ -1418,7 +1528,11 @@
       <c r="F27" s="19" t="n"/>
       <c r="G27" s="19" t="n"/>
       <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="n"/>
@@ -1429,7 +1543,11 @@
       <c r="F28" s="19" t="n"/>
       <c r="G28" s="19" t="n"/>
       <c r="H28" s="19" t="n"/>
-      <c r="I28" s="19" t="n"/>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n"/>
@@ -1440,7 +1558,11 @@
       <c r="F29" s="19" t="n"/>
       <c r="G29" s="19" t="n"/>
       <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n"/>
@@ -1451,7 +1573,11 @@
       <c r="F30" s="19" t="n"/>
       <c r="G30" s="19" t="n"/>
       <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n"/>
@@ -1462,7 +1588,11 @@
       <c r="F31" s="19" t="n"/>
       <c r="G31" s="19" t="n"/>
       <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n"/>
@@ -1473,7 +1603,11 @@
       <c r="F32" s="19" t="n"/>
       <c r="G32" s="19" t="n"/>
       <c r="H32" s="19" t="n"/>
-      <c r="I32" s="19" t="n"/>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n"/>
@@ -1484,7 +1618,11 @@
       <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
       <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n"/>
@@ -1495,7 +1633,11 @@
       <c r="F34" s="19" t="n"/>
       <c r="G34" s="19" t="n"/>
       <c r="H34" s="19" t="n"/>
-      <c r="I34" s="19" t="n"/>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n"/>
@@ -1506,7 +1648,11 @@
       <c r="F35" s="19" t="n"/>
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n"/>
@@ -1517,7 +1663,11 @@
       <c r="F36" s="19" t="n"/>
       <c r="G36" s="19" t="n"/>
       <c r="H36" s="19" t="n"/>
-      <c r="I36" s="19" t="n"/>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="n"/>
@@ -1528,7 +1678,11 @@
       <c r="F37" s="19" t="n"/>
       <c r="G37" s="19" t="n"/>
       <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="n"/>
@@ -1539,7 +1693,11 @@
       <c r="F38" s="19" t="n"/>
       <c r="G38" s="19" t="n"/>
       <c r="H38" s="19" t="n"/>
-      <c r="I38" s="19" t="n"/>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="n"/>
@@ -1550,7 +1708,11 @@
       <c r="F39" s="19" t="n"/>
       <c r="G39" s="19" t="n"/>
       <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="n"/>
@@ -1561,7 +1723,11 @@
       <c r="F40" s="19" t="n"/>
       <c r="G40" s="19" t="n"/>
       <c r="H40" s="19" t="n"/>
-      <c r="I40" s="19" t="n"/>
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="n"/>
@@ -1572,7 +1738,11 @@
       <c r="F41" s="19" t="n"/>
       <c r="G41" s="19" t="n"/>
       <c r="H41" s="19" t="n"/>
-      <c r="I41" s="19" t="n"/>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="n"/>
@@ -1583,7 +1753,11 @@
       <c r="F42" s="19" t="n"/>
       <c r="G42" s="19" t="n"/>
       <c r="H42" s="19" t="n"/>
-      <c r="I42" s="19" t="n"/>
+      <c r="I42" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="n"/>
@@ -1594,7 +1768,11 @@
       <c r="F43" s="19" t="n"/>
       <c r="G43" s="19" t="n"/>
       <c r="H43" s="19" t="n"/>
-      <c r="I43" s="19" t="n"/>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n"/>
@@ -1605,7 +1783,11 @@
       <c r="F44" s="19" t="n"/>
       <c r="G44" s="19" t="n"/>
       <c r="H44" s="19" t="n"/>
-      <c r="I44" s="19" t="n"/>
+      <c r="I44" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="n"/>
@@ -1616,7 +1798,11 @@
       <c r="F45" s="19" t="n"/>
       <c r="G45" s="19" t="n"/>
       <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
+      <c r="I45" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="n"/>
@@ -1627,7 +1813,11 @@
       <c r="F46" s="19" t="n"/>
       <c r="G46" s="19" t="n"/>
       <c r="H46" s="19" t="n"/>
-      <c r="I46" s="19" t="n"/>
+      <c r="I46" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="n"/>
@@ -1638,7 +1828,11 @@
       <c r="F47" s="19" t="n"/>
       <c r="G47" s="19" t="n"/>
       <c r="H47" s="19" t="n"/>
-      <c r="I47" s="19" t="n"/>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="n"/>
@@ -1649,7 +1843,11 @@
       <c r="F48" s="19" t="n"/>
       <c r="G48" s="19" t="n"/>
       <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
+      <c r="I48" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="18" t="n"/>
@@ -1660,7 +1858,11 @@
       <c r="F49" s="19" t="n"/>
       <c r="G49" s="19" t="n"/>
       <c r="H49" s="19" t="n"/>
-      <c r="I49" s="19" t="n"/>
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="n"/>
@@ -1671,7 +1873,11 @@
       <c r="F50" s="19" t="n"/>
       <c r="G50" s="19" t="n"/>
       <c r="H50" s="19" t="n"/>
-      <c r="I50" s="19" t="n"/>
+      <c r="I50" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="18" t="n"/>
@@ -1682,7 +1888,11 @@
       <c r="F51" s="19" t="n"/>
       <c r="G51" s="19" t="n"/>
       <c r="H51" s="19" t="n"/>
-      <c r="I51" s="19" t="n"/>
+      <c r="I51" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="18" t="n"/>
@@ -1693,7 +1903,11 @@
       <c r="F52" s="19" t="n"/>
       <c r="G52" s="19" t="n"/>
       <c r="H52" s="19" t="n"/>
-      <c r="I52" s="19" t="n"/>
+      <c r="I52" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="18" t="n"/>
@@ -1704,7 +1918,11 @@
       <c r="F53" s="19" t="n"/>
       <c r="G53" s="19" t="n"/>
       <c r="H53" s="19" t="n"/>
-      <c r="I53" s="19" t="n"/>
+      <c r="I53" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="18" t="n"/>
@@ -1715,7 +1933,11 @@
       <c r="F54" s="19" t="n"/>
       <c r="G54" s="19" t="n"/>
       <c r="H54" s="19" t="n"/>
-      <c r="I54" s="19" t="n"/>
+      <c r="I54" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="n"/>
@@ -1726,7 +1948,11 @@
       <c r="F55" s="19" t="n"/>
       <c r="G55" s="19" t="n"/>
       <c r="H55" s="19" t="n"/>
-      <c r="I55" s="19" t="n"/>
+      <c r="I55" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="18" t="n"/>
@@ -1737,7 +1963,11 @@
       <c r="F56" s="19" t="n"/>
       <c r="G56" s="19" t="n"/>
       <c r="H56" s="19" t="n"/>
-      <c r="I56" s="19" t="n"/>
+      <c r="I56" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="18" t="n"/>
@@ -1748,7 +1978,11 @@
       <c r="F57" s="19" t="n"/>
       <c r="G57" s="19" t="n"/>
       <c r="H57" s="19" t="n"/>
-      <c r="I57" s="19" t="n"/>
+      <c r="I57" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="18" t="n"/>
@@ -1759,7 +1993,11 @@
       <c r="F58" s="19" t="n"/>
       <c r="G58" s="19" t="n"/>
       <c r="H58" s="19" t="n"/>
-      <c r="I58" s="19" t="n"/>
+      <c r="I58" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="18" t="n"/>
@@ -1770,7 +2008,11 @@
       <c r="F59" s="19" t="n"/>
       <c r="G59" s="19" t="n"/>
       <c r="H59" s="19" t="n"/>
-      <c r="I59" s="19" t="n"/>
+      <c r="I59" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="18" t="n"/>
@@ -1781,7 +2023,11 @@
       <c r="F60" s="19" t="n"/>
       <c r="G60" s="19" t="n"/>
       <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
+      <c r="I60" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="18" t="n"/>
@@ -1792,7 +2038,11 @@
       <c r="F61" s="19" t="n"/>
       <c r="G61" s="19" t="n"/>
       <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
+      <c r="I61" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="18" t="n"/>
@@ -1803,7 +2053,11 @@
       <c r="F62" s="19" t="n"/>
       <c r="G62" s="19" t="n"/>
       <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
+      <c r="I62" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="18" t="n"/>
@@ -1814,7 +2068,11 @@
       <c r="F63" s="19" t="n"/>
       <c r="G63" s="19" t="n"/>
       <c r="H63" s="19" t="n"/>
-      <c r="I63" s="19" t="n"/>
+      <c r="I63" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="18" t="n"/>
@@ -1825,7 +2083,11 @@
       <c r="F64" s="19" t="n"/>
       <c r="G64" s="19" t="n"/>
       <c r="H64" s="19" t="n"/>
-      <c r="I64" s="19" t="n"/>
+      <c r="I64" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="18" t="n"/>
@@ -1836,7 +2098,11 @@
       <c r="F65" s="19" t="n"/>
       <c r="G65" s="19" t="n"/>
       <c r="H65" s="19" t="n"/>
-      <c r="I65" s="19" t="n"/>
+      <c r="I65" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="18" t="n"/>
@@ -1847,7 +2113,11 @@
       <c r="F66" s="19" t="n"/>
       <c r="G66" s="19" t="n"/>
       <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
+      <c r="I66" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="18" t="n"/>
@@ -1858,7 +2128,11 @@
       <c r="F67" s="19" t="n"/>
       <c r="G67" s="19" t="n"/>
       <c r="H67" s="19" t="n"/>
-      <c r="I67" s="19" t="n"/>
+      <c r="I67" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="18" t="n"/>
@@ -1869,7 +2143,11 @@
       <c r="F68" s="19" t="n"/>
       <c r="G68" s="19" t="n"/>
       <c r="H68" s="19" t="n"/>
-      <c r="I68" s="19" t="n"/>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="18" t="n"/>
@@ -1880,7 +2158,11 @@
       <c r="F69" s="19" t="n"/>
       <c r="G69" s="19" t="n"/>
       <c r="H69" s="19" t="n"/>
-      <c r="I69" s="19" t="n"/>
+      <c r="I69" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="18" t="n"/>
@@ -1891,7 +2173,11 @@
       <c r="F70" s="19" t="n"/>
       <c r="G70" s="19" t="n"/>
       <c r="H70" s="19" t="n"/>
-      <c r="I70" s="19" t="n"/>
+      <c r="I70" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="18" t="n"/>
@@ -1902,7 +2188,11 @@
       <c r="F71" s="19" t="n"/>
       <c r="G71" s="19" t="n"/>
       <c r="H71" s="19" t="n"/>
-      <c r="I71" s="19" t="n"/>
+      <c r="I71" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="18" t="n"/>
@@ -1913,7 +2203,11 @@
       <c r="F72" s="19" t="n"/>
       <c r="G72" s="19" t="n"/>
       <c r="H72" s="19" t="n"/>
-      <c r="I72" s="19" t="n"/>
+      <c r="I72" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="18" t="n"/>
@@ -1924,7 +2218,11 @@
       <c r="F73" s="19" t="n"/>
       <c r="G73" s="19" t="n"/>
       <c r="H73" s="19" t="n"/>
-      <c r="I73" s="19" t="n"/>
+      <c r="I73" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="18" t="n"/>
@@ -1935,7 +2233,11 @@
       <c r="F74" s="19" t="n"/>
       <c r="G74" s="19" t="n"/>
       <c r="H74" s="19" t="n"/>
-      <c r="I74" s="19" t="n"/>
+      <c r="I74" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="18" t="n"/>
@@ -1946,7 +2248,11 @@
       <c r="F75" s="19" t="n"/>
       <c r="G75" s="19" t="n"/>
       <c r="H75" s="19" t="n"/>
-      <c r="I75" s="19" t="n"/>
+      <c r="I75" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="18" t="n"/>
@@ -1957,7 +2263,11 @@
       <c r="F76" s="19" t="n"/>
       <c r="G76" s="19" t="n"/>
       <c r="H76" s="19" t="n"/>
-      <c r="I76" s="19" t="n"/>
+      <c r="I76" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="18" t="n"/>
@@ -1968,7 +2278,11 @@
       <c r="F77" s="19" t="n"/>
       <c r="G77" s="19" t="n"/>
       <c r="H77" s="19" t="n"/>
-      <c r="I77" s="19" t="n"/>
+      <c r="I77" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="18" t="n"/>
@@ -1979,7 +2293,11 @@
       <c r="F78" s="19" t="n"/>
       <c r="G78" s="19" t="n"/>
       <c r="H78" s="19" t="n"/>
-      <c r="I78" s="19" t="n"/>
+      <c r="I78" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="18" t="n"/>
@@ -1990,7 +2308,11 @@
       <c r="F79" s="19" t="n"/>
       <c r="G79" s="19" t="n"/>
       <c r="H79" s="19" t="n"/>
-      <c r="I79" s="19" t="n"/>
+      <c r="I79" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="18" t="n"/>
@@ -2001,7 +2323,11 @@
       <c r="F80" s="19" t="n"/>
       <c r="G80" s="19" t="n"/>
       <c r="H80" s="19" t="n"/>
-      <c r="I80" s="19" t="n"/>
+      <c r="I80" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="18" t="n"/>
@@ -2012,7 +2338,11 @@
       <c r="F81" s="19" t="n"/>
       <c r="G81" s="19" t="n"/>
       <c r="H81" s="19" t="n"/>
-      <c r="I81" s="19" t="n"/>
+      <c r="I81" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="18" t="n"/>
@@ -2023,7 +2353,11 @@
       <c r="F82" s="19" t="n"/>
       <c r="G82" s="19" t="n"/>
       <c r="H82" s="19" t="n"/>
-      <c r="I82" s="19" t="n"/>
+      <c r="I82" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="18" t="n"/>
@@ -2034,7 +2368,11 @@
       <c r="F83" s="19" t="n"/>
       <c r="G83" s="19" t="n"/>
       <c r="H83" s="19" t="n"/>
-      <c r="I83" s="19" t="n"/>
+      <c r="I83" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="18" t="n"/>
@@ -2045,7 +2383,11 @@
       <c r="F84" s="19" t="n"/>
       <c r="G84" s="19" t="n"/>
       <c r="H84" s="19" t="n"/>
-      <c r="I84" s="19" t="n"/>
+      <c r="I84" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="18" t="n"/>
@@ -2056,7 +2398,11 @@
       <c r="F85" s="19" t="n"/>
       <c r="G85" s="19" t="n"/>
       <c r="H85" s="19" t="n"/>
-      <c r="I85" s="19" t="n"/>
+      <c r="I85" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="18" t="n"/>
@@ -2067,7 +2413,11 @@
       <c r="F86" s="19" t="n"/>
       <c r="G86" s="19" t="n"/>
       <c r="H86" s="19" t="n"/>
-      <c r="I86" s="19" t="n"/>
+      <c r="I86" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="18" t="n"/>
@@ -2078,7 +2428,11 @@
       <c r="F87" s="19" t="n"/>
       <c r="G87" s="19" t="n"/>
       <c r="H87" s="19" t="n"/>
-      <c r="I87" s="19" t="n"/>
+      <c r="I87" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="18" t="n"/>
@@ -2089,7 +2443,11 @@
       <c r="F88" s="19" t="n"/>
       <c r="G88" s="19" t="n"/>
       <c r="H88" s="19" t="n"/>
-      <c r="I88" s="19" t="n"/>
+      <c r="I88" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="18" t="n"/>
@@ -2100,7 +2458,11 @@
       <c r="F89" s="19" t="n"/>
       <c r="G89" s="19" t="n"/>
       <c r="H89" s="19" t="n"/>
-      <c r="I89" s="19" t="n"/>
+      <c r="I89" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="18" t="n"/>
@@ -2111,7 +2473,11 @@
       <c r="F90" s="19" t="n"/>
       <c r="G90" s="19" t="n"/>
       <c r="H90" s="19" t="n"/>
-      <c r="I90" s="19" t="n"/>
+      <c r="I90" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="18" t="n"/>
@@ -2122,7 +2488,11 @@
       <c r="F91" s="19" t="n"/>
       <c r="G91" s="19" t="n"/>
       <c r="H91" s="19" t="n"/>
-      <c r="I91" s="19" t="n"/>
+      <c r="I91" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="n"/>
@@ -2133,7 +2503,11 @@
       <c r="F92" s="19" t="n"/>
       <c r="G92" s="19" t="n"/>
       <c r="H92" s="19" t="n"/>
-      <c r="I92" s="19" t="n"/>
+      <c r="I92" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="n"/>
@@ -2144,7 +2518,11 @@
       <c r="F93" s="19" t="n"/>
       <c r="G93" s="19" t="n"/>
       <c r="H93" s="19" t="n"/>
-      <c r="I93" s="19" t="n"/>
+      <c r="I93" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="n"/>
@@ -2155,7 +2533,11 @@
       <c r="F94" s="19" t="n"/>
       <c r="G94" s="19" t="n"/>
       <c r="H94" s="19" t="n"/>
-      <c r="I94" s="19" t="n"/>
+      <c r="I94" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="n"/>
@@ -2166,7 +2548,11 @@
       <c r="F95" s="19" t="n"/>
       <c r="G95" s="19" t="n"/>
       <c r="H95" s="19" t="n"/>
-      <c r="I95" s="19" t="n"/>
+      <c r="I95" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="18" t="n"/>
@@ -2177,7 +2563,11 @@
       <c r="F96" s="19" t="n"/>
       <c r="G96" s="19" t="n"/>
       <c r="H96" s="19" t="n"/>
-      <c r="I96" s="19" t="n"/>
+      <c r="I96" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="18" t="n"/>
@@ -2188,7 +2578,11 @@
       <c r="F97" s="19" t="n"/>
       <c r="G97" s="19" t="n"/>
       <c r="H97" s="19" t="n"/>
-      <c r="I97" s="19" t="n"/>
+      <c r="I97" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="n"/>
@@ -2199,7 +2593,11 @@
       <c r="F98" s="19" t="n"/>
       <c r="G98" s="19" t="n"/>
       <c r="H98" s="19" t="n"/>
-      <c r="I98" s="19" t="n"/>
+      <c r="I98" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="18" t="n"/>
@@ -2210,7 +2608,11 @@
       <c r="F99" s="19" t="n"/>
       <c r="G99" s="19" t="n"/>
       <c r="H99" s="19" t="n"/>
-      <c r="I99" s="19" t="n"/>
+      <c r="I99" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="18" t="n"/>
@@ -2221,7 +2623,11 @@
       <c r="F100" s="19" t="n"/>
       <c r="G100" s="19" t="n"/>
       <c r="H100" s="19" t="n"/>
-      <c r="I100" s="19" t="n"/>
+      <c r="I100" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="18" t="n"/>
@@ -2232,7 +2638,11 @@
       <c r="F101" s="19" t="n"/>
       <c r="G101" s="19" t="n"/>
       <c r="H101" s="19" t="n"/>
-      <c r="I101" s="19" t="n"/>
+      <c r="I101" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="18" t="n"/>
@@ -2243,7 +2653,11 @@
       <c r="F102" s="19" t="n"/>
       <c r="G102" s="19" t="n"/>
       <c r="H102" s="19" t="n"/>
-      <c r="I102" s="19" t="n"/>
+      <c r="I102" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="18" t="n"/>
@@ -2254,7 +2668,11 @@
       <c r="F103" s="19" t="n"/>
       <c r="G103" s="19" t="n"/>
       <c r="H103" s="19" t="n"/>
-      <c r="I103" s="19" t="n"/>
+      <c r="I103" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="18" t="n"/>
@@ -2265,7 +2683,11 @@
       <c r="F104" s="19" t="n"/>
       <c r="G104" s="19" t="n"/>
       <c r="H104" s="19" t="n"/>
-      <c r="I104" s="19" t="n"/>
+      <c r="I104" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="18" t="n"/>
@@ -2276,7 +2698,11 @@
       <c r="F105" s="19" t="n"/>
       <c r="G105" s="19" t="n"/>
       <c r="H105" s="19" t="n"/>
-      <c r="I105" s="19" t="n"/>
+      <c r="I105" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="18" t="n"/>
@@ -2287,7 +2713,11 @@
       <c r="F106" s="19" t="n"/>
       <c r="G106" s="19" t="n"/>
       <c r="H106" s="19" t="n"/>
-      <c r="I106" s="19" t="n"/>
+      <c r="I106" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="18" t="n"/>
@@ -2298,7 +2728,11 @@
       <c r="F107" s="19" t="n"/>
       <c r="G107" s="19" t="n"/>
       <c r="H107" s="19" t="n"/>
-      <c r="I107" s="19" t="n"/>
+      <c r="I107" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="18" t="n"/>
@@ -2309,7 +2743,11 @@
       <c r="F108" s="19" t="n"/>
       <c r="G108" s="19" t="n"/>
       <c r="H108" s="19" t="n"/>
-      <c r="I108" s="19" t="n"/>
+      <c r="I108" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="18" t="n"/>
@@ -2320,7 +2758,11 @@
       <c r="F109" s="19" t="n"/>
       <c r="G109" s="19" t="n"/>
       <c r="H109" s="19" t="n"/>
-      <c r="I109" s="19" t="n"/>
+      <c r="I109" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="18" t="n"/>
@@ -2331,7 +2773,11 @@
       <c r="F110" s="19" t="n"/>
       <c r="G110" s="19" t="n"/>
       <c r="H110" s="19" t="n"/>
-      <c r="I110" s="19" t="n"/>
+      <c r="I110" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="18" t="n"/>
@@ -2342,7 +2788,11 @@
       <c r="F111" s="19" t="n"/>
       <c r="G111" s="19" t="n"/>
       <c r="H111" s="19" t="n"/>
-      <c r="I111" s="19" t="n"/>
+      <c r="I111" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="18" t="n"/>
@@ -2353,7 +2803,11 @@
       <c r="F112" s="19" t="n"/>
       <c r="G112" s="19" t="n"/>
       <c r="H112" s="19" t="n"/>
-      <c r="I112" s="19" t="n"/>
+      <c r="I112" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="18" t="n"/>
@@ -2364,7 +2818,11 @@
       <c r="F113" s="19" t="n"/>
       <c r="G113" s="19" t="n"/>
       <c r="H113" s="19" t="n"/>
-      <c r="I113" s="19" t="n"/>
+      <c r="I113" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="18" t="n"/>
@@ -2375,7 +2833,11 @@
       <c r="F114" s="19" t="n"/>
       <c r="G114" s="19" t="n"/>
       <c r="H114" s="19" t="n"/>
-      <c r="I114" s="19" t="n"/>
+      <c r="I114" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="18" t="n"/>
@@ -2386,7 +2848,11 @@
       <c r="F115" s="19" t="n"/>
       <c r="G115" s="19" t="n"/>
       <c r="H115" s="19" t="n"/>
-      <c r="I115" s="19" t="n"/>
+      <c r="I115" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="18" t="n"/>
@@ -2397,7 +2863,11 @@
       <c r="F116" s="19" t="n"/>
       <c r="G116" s="19" t="n"/>
       <c r="H116" s="19" t="n"/>
-      <c r="I116" s="19" t="n"/>
+      <c r="I116" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="18" t="n"/>
@@ -2408,7 +2878,11 @@
       <c r="F117" s="19" t="n"/>
       <c r="G117" s="19" t="n"/>
       <c r="H117" s="19" t="n"/>
-      <c r="I117" s="19" t="n"/>
+      <c r="I117" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="18" t="n"/>
@@ -2419,7 +2893,11 @@
       <c r="F118" s="19" t="n"/>
       <c r="G118" s="19" t="n"/>
       <c r="H118" s="19" t="n"/>
-      <c r="I118" s="19" t="n"/>
+      <c r="I118" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="18" t="n"/>
@@ -2430,7 +2908,11 @@
       <c r="F119" s="19" t="n"/>
       <c r="G119" s="19" t="n"/>
       <c r="H119" s="19" t="n"/>
-      <c r="I119" s="19" t="n"/>
+      <c r="I119" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="18" t="n"/>
@@ -2441,7 +2923,11 @@
       <c r="F120" s="19" t="n"/>
       <c r="G120" s="19" t="n"/>
       <c r="H120" s="19" t="n"/>
-      <c r="I120" s="19" t="n"/>
+      <c r="I120" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="18" t="n"/>
@@ -2452,7 +2938,11 @@
       <c r="F121" s="19" t="n"/>
       <c r="G121" s="19" t="n"/>
       <c r="H121" s="19" t="n"/>
-      <c r="I121" s="19" t="n"/>
+      <c r="I121" s="21" t="inlineStr">
+        <is>
+          <t>heba.moustafa5@gmail.com</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
